--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,536 +33,352 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="109">
-  <si>
-    <t>* 주문전 유의사항</t>
-  </si>
-  <si>
-    <t>한번 등록하신 주문서를 임의대로 수정하실 경우 모든 책임은 고객에게 있습니다.</t>
-  </si>
-  <si>
-    <t>수정사항이 있으실 경우 반드시 고객센타로 전화를 주셔서 상담하시길 바랍니다.</t>
-  </si>
-  <si>
-    <t>단체명</t>
-  </si>
-  <si>
-    <t>사이즈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>수량</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사이즈(성인용)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기타사항</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>*기타 요청하고 싶은 부분 적으시면 되세요 별도 디자인 요청, 원하시는 모든것들을 적어주세요</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이니셜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>폰트</t>
-  </si>
-  <si>
-    <t>고딕체</t>
-  </si>
-  <si>
-    <t>필기체</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+  <si>
+    <t xml:space="preserve">* 주문전 유의사항</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한번 등록하신 주문서를 임의대로 수정하실 경우 모든 책임은 고객에게 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수정사항이 있으실 경우 반드시 고객센타로 전화를 주셔서 상담하시길 바랍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단체명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사이즈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수량</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사이즈(성인용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기타사항</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*기타 요청하고 싶은 부분 적으시면 되세요 별도 디자인 요청, 원하시는 모든것들을 적어주세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이니셜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폰트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고딕체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필기체</t>
   </si>
   <si>
     <t xml:space="preserve">제품디자인 </t>
   </si>
   <si>
-    <t>자수색상</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>위치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼손목</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>★이니셜 글자 수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>한글*한문</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>영어</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>특수문자(숫자포함)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10글자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고딕체</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고딕체/필기체</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>XS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>S</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>M</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>XL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2XL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3XL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>제품종류</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>*모르는 부분은 홈페이지 야구점퍼 안에 들어가서 보시거나  카톡 연결하셔서 물어보시면 되세요~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 왼팔 또는 오른팔에 학번이 들어가지 않을 경우 적지 않고 비워주시면 됩니다(없음,공란 등의 내용 기입 X)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 글씨체는 전부 통일 되오니 양해 부탁드려요(한명이라도 한글/한문/특수문자가 포함될 경우 전부 고딕체로)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 필기체의 경우 이니셜을 하시는 모든 분들이 영어로 넣으셔야 합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 왼소매 이니셜은 무료로 제공하는 서비스입니다. 
+    <t xml:space="preserve">자수색상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">왼손목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★이니셜 글자 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한글*한문</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수문자(숫자포함)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10글자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고딕체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고딕체/필기체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제품종류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*모르는 부분은 홈페이지 야구점퍼 안에 들어가서 보시거나  카톡 연결하셔서 물어보시면 되세요~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 왼팔 또는 오른팔에 학번이 들어가지 않을 경우 적지 않고 비워주시면 됩니다(없음,공란 등의 내용 기입 X)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 글씨체는 전부 통일 되오니 양해 부탁드려요(한명이라도 한글/한문/특수문자가 포함될 경우 전부 고딕체로)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 필기체의 경우 이니셜을 하시는 모든 분들이 영어로 넣으셔야 합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 왼소매 이니셜은 무료로 제공하는 서비스입니다. 
 따라서, 고객의 오기입 뿐만아니라 공장에서의 실수로 인한 인쇄오류 또한 무상 교환/환불이 불가합니다.
 공장의 실수는 매우 드물지만, 이에 대해 우려가 되시는 분은 이니셜 신청을 삼가하여 주시기 바랍니다.
 * 이니셜 A/S 비용: 10,000원</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 이니셜은 제일 작은 제품 사이즈부터 S-M-L-XL-2XL-3XL 순서대로 정리해주세요</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구점퍼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>항공점퍼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>코치자켓</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TJ-300 야상</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아노락</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>연락처</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>입금자명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>결제 방식</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">* 이니셜은 제일 작은 제품 사이즈부터 S-M-L-XL-2XL-3XL 순서대로 정리해주세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야구점퍼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항공점퍼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">코치자켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TJ-300 야상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아노락</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연락처</t>
+  </si>
+  <si>
+    <t xml:space="preserve">입금자명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결제 방식</t>
   </si>
   <si>
     <t xml:space="preserve">  카드결제</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  계좌이체</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">      유</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">      무</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문자 정보</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>세금계산서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">현금영수증
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">     (개인)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">현금영수증
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    (사업자)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래명세서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>간이영수증</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>필요 없음</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구점퍼/항공점퍼/코치자켓/TJ-300 야상/아노락/베이직 후리스-주문서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>베이직 후리스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">학번
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(들어갈 경우)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이니셜</t>
-  </si>
-  <si>
-    <t>구분</t>
-  </si>
-  <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>시안받으실 곳</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주문자 정보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">세금계산서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현금영수증
+     (개인)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현금영수증
+    (사업자)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거래명세서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">간이영수증</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필요 없음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야구점퍼/항공점퍼/코치자켓/TJ-300 야상/아노락/베이직 후리스-주문서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베이직 후리스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">학번
+(들어갈 경우)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이니셜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시안받으실 곳</t>
   </si>
   <si>
     <t xml:space="preserve">  카카오톡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  이메일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이메일은 이곳에 메일주소 작성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문자명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>배송주소</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>총수량</t>
-  </si>
-  <si>
-    <t>시안 이미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;*()_=~/)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">4XL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(추가비용문의)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">5XL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(추가비용문의)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이니셜에 한문 음과 뜻 적지 말아주세요!! 이니셜에는 이니셜만 적어주세요</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">지출증빙서류
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(현금영수증,세금계산서 중복 불가)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>현금영수증 번호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* 시안을 요청하여 픽스된 시안이 있거나 작년과 동일하게 진행 하시는 경우
+  </si>
+  <si>
+    <t xml:space="preserve">이메일은 이곳에 메일주소 작성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주문자명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배송주소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">총수량</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시안 이미지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;*()_=~/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4XL
+(추가비용문의)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5XL
+(추가비용문의)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이니셜에 한문 음과 뜻 적지 말아주세요!! 이니셜에는 이니셜만 적어주세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지출증빙서류
+(현금영수증,세금계산서 중복 불가)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현금영수증 번호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* 시안을 요청하여 픽스된 시안이 있거나 작년과 동일하게 진행 하시는 경우
   시안 이미지를 주문서와 함께 첨부해주세요.
 * 작년 시안일 경우 작년 시안 이미지 첨부 후 기타사항에 작년 시안과
   동일하게 한다고 적어주시면 됩니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>* 시안에서 변동되는 사항이 있을 경우 기타사항에 변경되는 내용을 작성해주세요.</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>seosanchang2008</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>장서산</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄱ</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>13354051717</t>
-  </si>
-  <si>
-    <t>1554643814</t>
-  </si>
-  <si>
-    <t>한양대 서울캠 창업학회</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>안현서</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-3627-7880</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>한양대창업학회</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-5320-8461</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서울시 성동구 살곶이 4길 1 103호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>검정(1180)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>jkychung47</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鍾桂怡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>vismirnova123</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사샤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>양진코코</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yangzhiying665</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>양지영</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>csengetimar2002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>체니</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>jyl070124</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>金艺霖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>camilla.leporace4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>☆밀라☆</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>celinehuang0503</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄佳琪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>lgrc101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캡플먼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ehmariame0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>~에덴~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+* 시안에서 변동되는 사항이 있을 경우 기타사항에 변경되는 내용을 작성해주세요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seosanchang2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장서산</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄱ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13354051717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1554643814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한양대 서울캠 창업학회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">안현서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010-3627-7880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한양대창업학회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010-5320-8461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서울시 성동구 살곶이 4길 1 103호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검정(1180)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jkychung47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鍾桂怡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vismirnova123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사샤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">양진코코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yangzhiying665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">양지영</t>
+  </si>
+  <si>
+    <t xml:space="preserve">csengetimar2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체니</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jyl070124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金艺霖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">camilla.leporace4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">☆밀라☆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">celinehuang0503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄佳琪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgrc101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">캡플먼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ehmariame0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~에덴~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aysel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아이셀</t>
   </si>
 </sst>
 </file>
@@ -3708,7 +3524,7 @@
         <v>6</v>
       </c>
       <c r="E23" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="8">
         <v>1</v>
@@ -4528,13 +4344,13 @@
         <v>5</v>
       </c>
       <c r="B80" s="120" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4543,13 +4359,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4573,13 +4389,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -4588,13 +4404,13 @@
         <v>9</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -4618,13 +4434,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -4633,13 +4449,13 @@
         <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -4647,9 +4463,15 @@
       <c r="A88" s="2">
         <v>13</v>
       </c>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5">

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t xml:space="preserve">아이셀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hyczy1230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신한</t>
   </si>
 </sst>
 </file>
@@ -3524,7 +3530,7 @@
         <v>6</v>
       </c>
       <c r="E23" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="8">
         <v>1</v>
@@ -4434,13 +4440,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -4449,13 +4455,13 @@
         <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -4464,13 +4470,13 @@
         <v>13</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -4478,9 +4484,15 @@
       <c r="A89" s="2">
         <v>14</v>
       </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5">

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -385,6 +385,15 @@
   </si>
   <si>
     <t xml:space="preserve">신한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021651557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">두월흥杜玥兴</t>
   </si>
 </sst>
 </file>
@@ -3538,7 +3547,9 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
+      <c r="J23" s="19">
+        <v>1</v>
+      </c>
       <c r="K23" s="41"/>
     </row>
     <row r="25" spans="1:12" ht="21" thickBot="1">
@@ -4499,9 +4510,15 @@
       <c r="A90" s="2">
         <v>15</v>
       </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5">

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -394,6 +394,12 @@
   </si>
   <si>
     <t xml:space="preserve">두월흥杜玥兴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">busraknss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busra~부스라</t>
   </si>
 </sst>
 </file>
@@ -3533,7 +3539,7 @@
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="8">
         <v>6</v>
@@ -4303,13 +4309,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C76" s="30" t="s">
         <v>25</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="E76" s="30"/>
     </row>
@@ -4318,12 +4324,14 @@
         <v>2</v>
       </c>
       <c r="B77" s="119" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="30"/>
+        <v>25</v>
+      </c>
+      <c r="D77" s="30" t="s">
+        <v>79</v>
+      </c>
       <c r="E77" s="30"/>
     </row>
     <row r="78" spans="1:12">
@@ -4331,14 +4339,12 @@
         <v>3</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C78" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D78" s="30" t="s">
-        <v>91</v>
-      </c>
+      <c r="D78" s="30" t="s"/>
       <c r="E78" s="30"/>
     </row>
     <row r="79" spans="1:12">
@@ -4346,13 +4352,13 @@
         <v>4</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C79" s="30" t="s">
         <v>26</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E79" s="30"/>
     </row>
@@ -4361,13 +4367,13 @@
         <v>5</v>
       </c>
       <c r="B80" s="120" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4376,13 +4382,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4391,13 +4397,13 @@
         <v>7</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -4406,13 +4412,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -4421,13 +4427,13 @@
         <v>9</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -4436,13 +4442,13 @@
         <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -4451,13 +4457,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -4466,13 +4472,13 @@
         <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -4481,13 +4487,13 @@
         <v>13</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -4496,13 +4502,13 @@
         <v>14</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -4511,13 +4517,13 @@
         <v>15</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -4525,9 +4531,15 @@
       <c r="A91" s="2">
         <v>16</v>
       </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5">

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t xml:space="preserve">Busra~부스라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">youlinaiweiqi</t>
   </si>
 </sst>
 </file>
@@ -3542,7 +3545,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="8">
         <v>6</v>
@@ -4352,14 +4355,12 @@
         <v>4</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C79" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="30" t="s">
-        <v>91</v>
-      </c>
+      <c r="D79" s="30" t="s"/>
       <c r="E79" s="30"/>
     </row>
     <row r="80" spans="1:12">
@@ -4367,13 +4368,13 @@
         <v>5</v>
       </c>
       <c r="B80" s="120" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4382,13 +4383,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4397,13 +4398,13 @@
         <v>7</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -4412,13 +4413,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E83" s="2"/>
     </row>
@@ -4427,13 +4428,13 @@
         <v>9</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E84" s="2"/>
     </row>
@@ -4442,13 +4443,13 @@
         <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E85" s="2"/>
     </row>
@@ -4457,13 +4458,13 @@
         <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E86" s="2"/>
     </row>
@@ -4472,13 +4473,13 @@
         <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E87" s="2"/>
     </row>
@@ -4487,13 +4488,13 @@
         <v>13</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E88" s="2"/>
     </row>
@@ -4502,13 +4503,13 @@
         <v>14</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E89" s="2"/>
     </row>
@@ -4517,13 +4518,13 @@
         <v>15</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E90" s="2"/>
     </row>
@@ -4532,13 +4533,13 @@
         <v>16</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E91" s="2"/>
     </row>
@@ -4546,9 +4547,15 @@
       <c r="A92" s="2">
         <v>17</v>
       </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5">

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t xml:space="preserve">youlinaiweiqi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유리노</t>
   </si>
 </sst>
 </file>
@@ -4355,12 +4358,14 @@
         <v>4</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C79" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="30" t="s"/>
+      <c r="D79" s="30" t="s">
+        <v>91</v>
+      </c>
       <c r="E79" s="30"/>
     </row>
     <row r="80" spans="1:12">
@@ -4368,13 +4373,13 @@
         <v>5</v>
       </c>
       <c r="B80" s="120" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -4383,13 +4388,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E81" s="2"/>
     </row>
@@ -4398,13 +4403,13 @@
         <v>7</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E82" s="2"/>
     </row>
@@ -4413,13 +4418,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="E83" s="2"/>
     </row>

--- a/vendor-order/TJ300_한글한자특수문자.xlsx
+++ b/vendor-order/TJ300_한글한자특수문자.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t xml:space="preserve">* 주문전 유의사항</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">시안 이미지</t>
   </si>
   <si>
-    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;amp;amp;amp;*()_=~/)</t>
+    <t xml:space="preserve">* 특수문자 이니셜 같은 경우에는 기본적인 문자만 가능해요(^!@#$%&amp;amp;amp;amp;amp;amp;amp;amp;amp;*()_=~/)</t>
   </si>
   <si>
     <t xml:space="preserve">4XL
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t xml:space="preserve">유리노</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bk부스라</t>
   </si>
 </sst>
 </file>
@@ -4321,7 +4324,7 @@
         <v>25</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E76" s="30"/>
     </row>
